--- a/lista_clase.xlsx
+++ b/lista_clase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\pj_sa_202601\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB7E2F4-7C25-4B07-A0CC-FAACDE6196BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F59F81-3FF5-48BC-9CA9-D0DA3BF10CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t xml:space="preserve">DOCENTE: </t>
   </si>
@@ -1497,7 +1497,9 @@
       <c r="I11" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="43"/>
+      <c r="J11" s="43" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="39">
@@ -1525,7 +1527,9 @@
       <c r="I12" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="43"/>
+      <c r="J12" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="39">
@@ -1551,7 +1555,9 @@
       <c r="I13" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="43"/>
+      <c r="J13" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="39">
@@ -1579,7 +1585,9 @@
       <c r="I14" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="43"/>
+      <c r="J14" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39">
@@ -1607,7 +1615,9 @@
       <c r="I15" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="43"/>
+      <c r="J15" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="39">
@@ -1635,7 +1645,9 @@
       <c r="I16" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="43"/>
+      <c r="J16" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="39">
@@ -1663,7 +1675,9 @@
       <c r="I17" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="43"/>
+      <c r="J17" s="43" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C12:D15">
